--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.03125777900766041</v>
       </c>
       <c r="C2" t="n">
-        <v>31063860</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31063860</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>22723231</v>
+        <v>4213502</v>
       </c>
       <c r="L2" t="n">
-        <v>13639730</v>
+        <v>2318850</v>
       </c>
       <c r="M2" t="n">
-        <v>3625448</v>
+        <v>572803</v>
       </c>
       <c r="N2" t="n">
-        <v>224616</v>
+        <v>28298</v>
       </c>
       <c r="O2" t="n">
-        <v>2123574</v>
+        <v>353911</v>
       </c>
       <c r="P2" t="n">
-        <v>849140</v>
+        <v>148815</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999593496322632</v>
+        <v>0.9999064803123474</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9231270551681519</v>
+        <v>0.8558244705200195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.845552384853363</v>
+        <v>0.7187339663505554</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7762916088104248</v>
+        <v>0.6133726835250854</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6234380602836609</v>
+        <v>0.3949752151966095</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8351728916168213</v>
+        <v>0.6960887312889099</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8780652284622192</v>
+        <v>0.7690975666046143</v>
       </c>
       <c r="X2" t="n">
-        <v>31063860</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31063860</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>21956039</v>
+        <v>4098451</v>
       </c>
       <c r="AG2" t="n">
-        <v>12547940</v>
+        <v>2160035</v>
       </c>
       <c r="AH2" t="n">
-        <v>3229049</v>
+        <v>523313</v>
       </c>
       <c r="AI2" t="n">
-        <v>196806</v>
+        <v>26078</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1941860</v>
+        <v>326935</v>
       </c>
       <c r="AK2" t="n">
-        <v>795961</v>
+        <v>139695</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.889315664768219</v>
+        <v>0.8300260305404663</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.7832459211349487</v>
+        <v>0.6741499304771423</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6973374485969543</v>
+        <v>0.565066933631897</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4453732967376709</v>
+        <v>0.2950734198093414</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7644305229187012</v>
+        <v>0.6435044407844543</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.8237075805664062</v>
+        <v>0.7228233218193054</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.008287393333615061</v>
       </c>
       <c r="C3" t="n">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="D3" t="n">
-        <v>22723231</v>
+        <v>4213502</v>
       </c>
       <c r="E3" t="n">
-        <v>1743914</v>
+        <v>641189</v>
       </c>
       <c r="F3" t="n">
-        <v>87235</v>
+        <v>33458</v>
       </c>
       <c r="G3" t="n">
-        <v>17161</v>
+        <v>5769</v>
       </c>
       <c r="H3" t="n">
-        <v>1683</v>
+        <v>1054</v>
       </c>
       <c r="I3" t="n">
-        <v>457</v>
+        <v>173</v>
       </c>
       <c r="J3" t="n">
-        <v>49286877</v>
+        <v>9857047</v>
       </c>
       <c r="K3" t="n">
-        <v>53885739</v>
+        <v>10465250</v>
       </c>
       <c r="L3" t="n">
-        <v>61747081</v>
+        <v>11923746</v>
       </c>
       <c r="M3" t="n">
-        <v>74660999</v>
+        <v>14777840</v>
       </c>
       <c r="N3" t="n">
-        <v>79773242</v>
+        <v>15938293</v>
       </c>
       <c r="O3" t="n">
-        <v>77388164</v>
+        <v>15406446</v>
       </c>
       <c r="P3" t="n">
-        <v>79267497</v>
+        <v>15832329</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9246860146522522</v>
+        <v>0.8607192039489746</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8464783430099487</v>
+        <v>0.7158699035644531</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7802980542182922</v>
+        <v>0.6149221062660217</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5069331526756287</v>
+        <v>0.3188147842884064</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8344974517822266</v>
+        <v>0.6947100162506104</v>
       </c>
       <c r="W3" t="n">
-        <v>0.878494918346405</v>
+        <v>0.7694952487945557</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>21956039</v>
+        <v>4098451</v>
       </c>
       <c r="Z3" t="n">
-        <v>2441958</v>
+        <v>740530</v>
       </c>
       <c r="AA3" t="n">
-        <v>113298</v>
+        <v>38881</v>
       </c>
       <c r="AB3" t="n">
-        <v>58886</v>
+        <v>15351</v>
       </c>
       <c r="AC3" t="n">
-        <v>3367</v>
+        <v>1917</v>
       </c>
       <c r="AD3" t="n">
-        <v>448</v>
+        <v>197</v>
       </c>
       <c r="AE3" t="n">
-        <v>49288140</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>53045353</v>
+        <v>10335786</v>
       </c>
       <c r="AG3" t="n">
-        <v>60766003</v>
+        <v>11787142</v>
       </c>
       <c r="AH3" t="n">
-        <v>74304274</v>
+        <v>14736100</v>
       </c>
       <c r="AI3" t="n">
-        <v>79663828</v>
+        <v>15919340</v>
       </c>
       <c r="AJ3" t="n">
-        <v>77208856</v>
+        <v>15379844</v>
       </c>
       <c r="AK3" t="n">
-        <v>79215061</v>
+        <v>15823439</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8934663534164429</v>
+        <v>0.8372169733047485</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7787221074104309</v>
+        <v>0.6668409109115601</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6949818730354309</v>
+        <v>0.5617930293083191</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4441691040992737</v>
+        <v>0.2938035130500793</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7630895972251892</v>
+        <v>0.6417574882507324</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.8234775066375732</v>
+        <v>0.7223374247550964</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.07326137193158536</v>
       </c>
       <c r="C4" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>1792372</v>
+        <v>674069</v>
       </c>
       <c r="E4" t="n">
-        <v>13639730</v>
+        <v>2318850</v>
       </c>
       <c r="F4" t="n">
-        <v>614404</v>
+        <v>214718</v>
       </c>
       <c r="G4" t="n">
-        <v>22017</v>
+        <v>8450</v>
       </c>
       <c r="H4" t="n">
-        <v>40939</v>
+        <v>20823</v>
       </c>
       <c r="I4" t="n">
-        <v>3885</v>
+        <v>2211</v>
       </c>
       <c r="J4" t="n">
-        <v>1263</v>
+        <v>581</v>
       </c>
       <c r="K4" t="n">
-        <v>1892265</v>
+        <v>709823</v>
       </c>
       <c r="L4" t="n">
-        <v>2491417</v>
+        <v>907448</v>
       </c>
       <c r="M4" t="n">
-        <v>1044766</v>
+        <v>361055</v>
       </c>
       <c r="N4" t="n">
-        <v>135670</v>
+        <v>43347</v>
       </c>
       <c r="O4" t="n">
-        <v>419102</v>
+        <v>154517</v>
       </c>
       <c r="P4" t="n">
-        <v>117918</v>
+        <v>44678</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999796748161316</v>
+        <v>0.9999532103538513</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9239059090614319</v>
+        <v>0.8582648634910583</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8460150957107544</v>
+        <v>0.7172989845275879</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7782896757125854</v>
+        <v>0.6141464114189148</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5591816306114197</v>
+        <v>0.3528318703174591</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8348350524902344</v>
+        <v>0.6953986883163452</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8782800436019897</v>
+        <v>0.7692963480949402</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2585423</v>
+        <v>792041</v>
       </c>
       <c r="Z4" t="n">
-        <v>12547940</v>
+        <v>2160035</v>
       </c>
       <c r="AA4" t="n">
-        <v>847483</v>
+        <v>238897</v>
       </c>
       <c r="AB4" t="n">
-        <v>55399</v>
+        <v>15541</v>
       </c>
       <c r="AC4" t="n">
-        <v>69956</v>
+        <v>29154</v>
       </c>
       <c r="AD4" t="n">
-        <v>7301</v>
+        <v>3538</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2732651</v>
+        <v>839287</v>
       </c>
       <c r="AG4" t="n">
-        <v>3472495</v>
+        <v>1044052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1401491</v>
+        <v>402795</v>
       </c>
       <c r="AI4" t="n">
-        <v>245084</v>
+        <v>62300</v>
       </c>
       <c r="AJ4" t="n">
-        <v>598410</v>
+        <v>181119</v>
       </c>
       <c r="AK4" t="n">
-        <v>170354</v>
+        <v>53568</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8913861513137817</v>
+        <v>0.8336060047149658</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7809774279594421</v>
+        <v>0.6704755425453186</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6961576342582703</v>
+        <v>0.5634252429008484</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4447703659534454</v>
+        <v>0.2944370806217194</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.763759434223175</v>
+        <v>0.6426298022270203</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.8235925436019897</v>
+        <v>0.7225802540779114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>60058</v>
+        <v>22927</v>
       </c>
       <c r="E5" t="n">
-        <v>657538</v>
+        <v>228092</v>
       </c>
       <c r="F5" t="n">
-        <v>3625448</v>
+        <v>572803</v>
       </c>
       <c r="G5" t="n">
-        <v>52751</v>
+        <v>15984</v>
       </c>
       <c r="H5" t="n">
-        <v>233357</v>
+        <v>83170</v>
       </c>
       <c r="I5" t="n">
-        <v>16906</v>
+        <v>8443</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1850765</v>
+        <v>681825</v>
       </c>
       <c r="L5" t="n">
-        <v>2473772</v>
+        <v>920356</v>
       </c>
       <c r="M5" t="n">
-        <v>1020787</v>
+        <v>358702</v>
       </c>
       <c r="N5" t="n">
-        <v>218472</v>
+        <v>60462</v>
       </c>
       <c r="O5" t="n">
-        <v>421160</v>
+        <v>155526</v>
       </c>
       <c r="P5" t="n">
-        <v>117445</v>
+        <v>44578</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999842643737793</v>
+        <v>0.9999638199806213</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9534170627593994</v>
+        <v>0.9134030342102051</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9382070302963257</v>
+        <v>0.8862627148628235</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9742937088012695</v>
+        <v>0.9552122354507446</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9955925941467285</v>
+        <v>0.993540346622467</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9895427227020264</v>
+        <v>0.9807072281837463</v>
       </c>
       <c r="W5" t="n">
-        <v>0.997070848941803</v>
+        <v>0.9944459199905396</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>92185</v>
+        <v>32315</v>
       </c>
       <c r="Z5" t="n">
-        <v>896478</v>
+        <v>252709</v>
       </c>
       <c r="AA5" t="n">
-        <v>3229049</v>
+        <v>523313</v>
       </c>
       <c r="AB5" t="n">
-        <v>73278</v>
+        <v>17597</v>
       </c>
       <c r="AC5" t="n">
-        <v>327191</v>
+        <v>94225</v>
       </c>
       <c r="AD5" t="n">
-        <v>28054</v>
+        <v>11346</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2617957</v>
+        <v>796876</v>
       </c>
       <c r="AG5" t="n">
-        <v>3565562</v>
+        <v>1079171</v>
       </c>
       <c r="AH5" t="n">
-        <v>1417186</v>
+        <v>408192</v>
       </c>
       <c r="AI5" t="n">
-        <v>246282</v>
+        <v>62682</v>
       </c>
       <c r="AJ5" t="n">
-        <v>602874</v>
+        <v>182502</v>
       </c>
       <c r="AK5" t="n">
-        <v>170624</v>
+        <v>53698</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9334104061126709</v>
+        <v>0.8981877565383911</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9124096632003784</v>
+        <v>0.8678798675537109</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9649208784103394</v>
+        <v>0.9495353698730469</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9938848614692688</v>
+        <v>0.9922228455543518</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9850497245788574</v>
+        <v>0.9773732423782349</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9957564473152161</v>
+        <v>0.9933252334594727</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>392</v>
+        <v>155</v>
       </c>
       <c r="D6" t="n">
-        <v>39328</v>
+        <v>12467</v>
       </c>
       <c r="E6" t="n">
-        <v>47274</v>
+        <v>15121</v>
       </c>
       <c r="F6" t="n">
-        <v>87899</v>
+        <v>19544</v>
       </c>
       <c r="G6" t="n">
-        <v>224616</v>
+        <v>28298</v>
       </c>
       <c r="H6" t="n">
-        <v>38831</v>
+        <v>11405</v>
       </c>
       <c r="I6" t="n">
-        <v>4748</v>
+        <v>1770</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>53118</v>
+        <v>13580</v>
       </c>
       <c r="Z6" t="n">
-        <v>57326</v>
+        <v>16627</v>
       </c>
       <c r="AA6" t="n">
-        <v>79236</v>
+        <v>18486</v>
       </c>
       <c r="AB6" t="n">
-        <v>196806</v>
+        <v>26078</v>
       </c>
       <c r="AC6" t="n">
-        <v>50187</v>
+        <v>11941</v>
       </c>
       <c r="AD6" t="n">
-        <v>6415</v>
+        <v>2048</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="E7" t="n">
-        <v>40606</v>
+        <v>21907</v>
       </c>
       <c r="F7" t="n">
-        <v>246951</v>
+        <v>89106</v>
       </c>
       <c r="G7" t="n">
-        <v>41170</v>
+        <v>12065</v>
       </c>
       <c r="H7" t="n">
-        <v>2123574</v>
+        <v>353911</v>
       </c>
       <c r="I7" t="n">
-        <v>91922</v>
+        <v>32081</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1680</v>
+        <v>1284</v>
       </c>
       <c r="Z7" t="n">
-        <v>72505</v>
+        <v>31973</v>
       </c>
       <c r="AA7" t="n">
-        <v>347168</v>
+        <v>100506</v>
       </c>
       <c r="AB7" t="n">
-        <v>53385</v>
+        <v>12300</v>
       </c>
       <c r="AC7" t="n">
-        <v>1941860</v>
+        <v>326935</v>
       </c>
       <c r="AD7" t="n">
-        <v>128136</v>
+        <v>36439</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>2085</v>
+        <v>1139</v>
       </c>
       <c r="F8" t="n">
-        <v>8277</v>
+        <v>4229</v>
       </c>
       <c r="G8" t="n">
-        <v>2571</v>
+        <v>1079</v>
       </c>
       <c r="H8" t="n">
-        <v>104292</v>
+        <v>38065</v>
       </c>
       <c r="I8" t="n">
-        <v>849140</v>
+        <v>148815</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>245</v>
+        <v>67</v>
       </c>
       <c r="Z8" t="n">
-        <v>4228</v>
+        <v>2213</v>
       </c>
       <c r="AA8" t="n">
-        <v>14306</v>
+        <v>6025</v>
       </c>
       <c r="AB8" t="n">
-        <v>4136</v>
+        <v>1511</v>
       </c>
       <c r="AC8" t="n">
-        <v>147709</v>
+        <v>43882</v>
       </c>
       <c r="AD8" t="n">
-        <v>795961</v>
+        <v>139695</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
